--- a/samplesheet_set3.xlsx
+++ b/samplesheet_set3.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oregonstateuniversity-my.sharepoint.com/personal/nguyen23_oregonstate_edu/Documents/Canine_Cancer/RNA-Seq/Set3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{97D1085A-D7AE-7F40-8CB3-4A2710AA7AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89EE4E10-CCCD-CD4C-BFA2-1D28E0E53ECF}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{97D1085A-D7AE-7F40-8CB3-4A2710AA7AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B407F364-608C-6C43-9FED-D693BCF87EE0}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="500" windowWidth="17000" windowHeight="16360" xr2:uid="{EED18B7A-ED6D-2A40-91F9-E2996ACB05DD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{EED18B7A-ED6D-2A40-91F9-E2996ACB05DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$202</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="405">
   <si>
     <t>sample</t>
   </si>
@@ -1149,12 +1149,132 @@
   <si>
     <t>Penn1B_S122</t>
   </si>
+  <si>
+    <t>Rothery1B_set2</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s182-index--CGATTCTGATTG-AGCTTATGCTTG-Rothery1B_set2_S182_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s183-index--TGGGTCTTCGCC-TGGGTATTAGAA-Rothery2B_set2_S183_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s184-index--GTCGTCGAACGC-GTAGTAGCCAGA-Foster1B_set2_S184_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s185-index--GAAGTGCCCCCA-GCCGTGAAAAAC-Foster2B_set2_S185_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s186-index--GCCGGGAATAAG-GAAGGGCCTCCG-Barrow1B_set2_S186_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s187-index--TTCTGGTCCCAG-TTATGGTAAACG-Strople1B_set2_S187_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s188-index--TCGAAGTGCTGT-TAGCCGTGATGT-Wells1B_set2_S188_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s189-index--GTATCTTGTCAC-GTCTATTGTACA-Woolsey1B_set2_S189_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s190-index--GCTACTTTGGGG-GATCATTTGGGG-McFarland1B_set2_S190_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s191-index--ATTGATCAAGCT-CTTGCTACCGAT-Porbandawalla1B_set2_S191_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s192-index--AGGCAAGAACGT-CGGACCGCCAGT-Barrow1B_set3_S192_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s193-index--GTGCGGCCGAGT-GTGAGGAAGCGT-Foster1B_set3_S193_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s194-index--GCGGAGCACCCA-GAGGCGACAAAC-Foster2B_set3_S194_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s195-index--CGCTCGGTGGGA-AGATAGGTGGGC-McFarland1B_set3_S195_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s196-index--ACCCTAGATCGC-CAAATCGCTAGA-Porbandarwalla1B_set3_S196_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s197-index--CAGAACGAATCC-ACGCCAGCCTAA-Rothery1B_set3_S197_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s198-index--CCGCAATGAACT-AAGACCTGCCAT-Rothery2B_set3_S198_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s199-index--TGAGAGGGGTTC-TGCGCGGGGTTA-Strople1B_set3_S199_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s200-index--CATACTTATTTG-ACTCATTCTTTG-Wells1B_set3_S200_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>/nfs2/hts/nextseq/260922_VH00571_741_222KMC2NX/L1-dual-12bp-1mm/lane1-s201-index--CATCGACGTACG-ACTAGCAGTCAG-Woolsey1B_set3_S201_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>Rothery2B_set2</t>
+  </si>
+  <si>
+    <t>Foster1B_set2</t>
+  </si>
+  <si>
+    <t>Foster2B_set2</t>
+  </si>
+  <si>
+    <t>Barrow1B_set2</t>
+  </si>
+  <si>
+    <t>Strople1B_set2</t>
+  </si>
+  <si>
+    <t>Wells1B_set2</t>
+  </si>
+  <si>
+    <t>Woolsey1B_set2</t>
+  </si>
+  <si>
+    <t>McFarland1B_set2</t>
+  </si>
+  <si>
+    <t>Porbandawalla1B_set2</t>
+  </si>
+  <si>
+    <t>Barrow1B_set3</t>
+  </si>
+  <si>
+    <t>Foster1B_set3</t>
+  </si>
+  <si>
+    <t>Foster2B_set3</t>
+  </si>
+  <si>
+    <t>McFarland1B_set3</t>
+  </si>
+  <si>
+    <t>Porbandarwalla1B_set3</t>
+  </si>
+  <si>
+    <t>Rothery1B_set3</t>
+  </si>
+  <si>
+    <t>Rothery2B_set3</t>
+  </si>
+  <si>
+    <t>Strople1B_set3</t>
+  </si>
+  <si>
+    <t>Wells1B_set3</t>
+  </si>
+  <si>
+    <t>Woolsey1B_set3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1166,6 +1286,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1189,9 +1316,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1528,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49253A0A-C97B-BD49-9C8A-11C2D024E84F}">
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" customWidth="1"/>
@@ -3541,8 +3671,237 @@
         <v>4</v>
       </c>
     </row>
+    <row r="183" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D183" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>386</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D184" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>387</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D185" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>388</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D186" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>389</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D187" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>390</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D188" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D189" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>392</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D190" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>393</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D191" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>394</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D192" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>395</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D193" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>396</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D194" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>397</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D195" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>398</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D196" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>399</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D197" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>400</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D198" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>401</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D199" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>402</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D200" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>403</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D201" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>404</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D202" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B203" s="2"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B204" s="2"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B205" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A185" xr:uid="{49253A0A-C97B-BD49-9C8A-11C2D024E84F}"/>
+  <autoFilter ref="A1:A202" xr:uid="{49253A0A-C97B-BD49-9C8A-11C2D024E84F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>